--- a/forms/trg/Formulir_TRG_drg.xlsx
+++ b/forms/trg/Formulir_TRG_drg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Ardiati Arief, ST. MTM. Ph.D</t>
+          <t>Dr. Ishak Salim, S.IP., MA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>35408556600</t>
+          <t>57216707194</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Novy N.R.A. Mokobombang, S.T., Ms.T.M., Ph.D</t>
+          <t>Prof. Ardiati Arief, ST. MTM. Ph.D</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -968,15 +968,11 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-5706-939X</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57194163898</t>
+          <t>35408556600</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -991,12 +987,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr.Ing.Ir. Venny Veronica Natalia ST., MT</t>
+          <t>Novy N.R.A. Mokobombang, S.T., Ms.T.M., Ph.D</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,11 +1005,15 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5706-939X</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57210944664</t>
+          <t>57194163898</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Nurlela, S.Sos.,M.Si.</t>
+          <t>Dr.Ing.Ir. Venny Veronica Natalia ST., MT</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1048,7 +1048,11 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57210944664</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1061,12 +1065,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Icha Musywirah Hamka, S.Sos.,M.Si</t>
+          <t>Andi Nurlela, S.Sos.,M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1079,11 +1083,7 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0009-0001-4163-1744</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1098,17 +1098,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Faizuddin, S.Pd.I, M.Ed., PhD</t>
+          <t>Icha Musywirah Hamka, S.Sos.,M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>INTI International University, Malaysia.</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1116,13 +1116,13 @@
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0009-0001-4163-1744</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57200140000</t>
-        </is>
-      </c>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1135,17 +1135,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Sudirman Nasir, S.Ked., MWH., Ph.D</t>
+          <t>Ahmad Faizuddin, S.Pd.I, M.Ed., PhD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>INTI International University, Malaysia.</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1153,15 +1153,11 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-9735-1178</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>24341795900</t>
+          <t>57200140000</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1176,12 +1172,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Ida Arianti Said</t>
+          <t>Sudirman Nasir, S.Ked., MWH., Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1194,9 +1190,17 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-9735-1178</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>24341795900</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1209,12 +1213,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muh. Ilham</t>
+          <t>Ida Arianti Said</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1242,12 +1246,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Hasbullah</t>
+          <t>Muh. Ilham</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1275,12 +1279,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Tiara Ramadhani Sinjar</t>
+          <t>Hasbullah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1308,12 +1312,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Junaidi</t>
+          <t>Tiara Ramadhani Sinjar</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1321,11 +1325,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>DRG Team</t>
-        </is>
-      </c>
+      <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1343,10 +1343,26 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Junaidi</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>DRG Team</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1354,7 +1370,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1543,15 +1563,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
